--- a/AAAGameData/DataTables/TaskReward.xlsx
+++ b/AAAGameData/DataTables/TaskReward.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27000" windowHeight="17175"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>#</t>
   </si>
@@ -49,6 +49,9 @@
     <t>Reward</t>
   </si>
   <si>
+    <t>RewardMulti</t>
+  </si>
+  <si>
     <t>TaskType</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t>奖励值</t>
+  </si>
+  <si>
+    <t>奖励倍数</t>
   </si>
   <si>
     <t>任务类型（1.看广告 2.通关数）</t>
@@ -694,7 +700,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -706,7 +712,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1240,19 +1245,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="7"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.8571428571429" customWidth="1"/>
     <col min="3" max="4" width="24.5714285714286" customWidth="1"/>
     <col min="5" max="5" width="25.7142857142857" customWidth="1"/>
-    <col min="6" max="6" width="20.2857142857143" customWidth="1"/>
-    <col min="7" max="7" width="19.7142857142857" customWidth="1"/>
-    <col min="8" max="8" width="30.1428571428571" customWidth="1"/>
-    <col min="9" max="9" width="64" customWidth="1"/>
+    <col min="6" max="7" width="20.2857142857143" customWidth="1"/>
+    <col min="8" max="8" width="19.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="30.1428571428571" customWidth="1"/>
+    <col min="10" max="10" width="64" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1260,7 +1265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1276,44 +1281,53 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:8">
+    <row r="4" ht="20" customHeight="1" spans="1:9">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:8">
+    <row r="5" ht="20" customHeight="1" spans="1:9">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1327,10 +1341,13 @@
       <c r="F5" s="4">
         <v>1</v>
       </c>
-      <c r="G5" s="4"/>
+      <c r="G5" s="4">
+        <v>1</v>
+      </c>
       <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
-    <row r="6" customHeight="1" spans="1:8">
+    <row r="6" customHeight="1" spans="1:9">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1339,15 +1356,18 @@
         <v>8</v>
       </c>
       <c r="E6" s="4">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4">
         <v>2</v>
       </c>
-      <c r="G6" s="4"/>
       <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1356,15 +1376,18 @@
         <v>18</v>
       </c>
       <c r="E7" s="4">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4">
         <v>2</v>
       </c>
-      <c r="G7" s="4"/>
       <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1373,15 +1396,18 @@
         <v>30</v>
       </c>
       <c r="E8" s="4">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4">
         <v>2</v>
       </c>
-      <c r="G8" s="4"/>
       <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1390,13 +1416,16 @@
         <v>40</v>
       </c>
       <c r="E9" s="4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F9" s="4">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="B10">
         <v>6</v>
       </c>
@@ -1404,37 +1433,23 @@
         <v>50</v>
       </c>
       <c r="E10" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F10" s="4">
+        <v>10</v>
+      </c>
+      <c r="G10" s="4">
         <v>2</v>
       </c>
-      <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11">
-        <v>7</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="5">
-        <v>60</v>
-      </c>
-      <c r="E11" s="4">
-        <v>100</v>
-      </c>
-      <c r="F11" s="4">
-        <v>2</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="I10" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E1:AA1">
+    <dataValidation type="list" allowBlank="1" sqref="E1 F1 G1:AB1">
       <formula1>"i18n"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I3:AA3">
+    <dataValidation type="list" sqref="J3:AB3">
       <formula1>"double,int,bool,string,float,enum,string[],uint,short,Vector2[],Vector3Int[],int4[],int4,Vector3Int,Vector3,Vector4[],Vector2,Vector4,Color,Color32,Vector2Int,Vector3[],Vector2Int[],Type,long[],bool[],int[],float[],double[],float[][],decimal,double[][]"</formula1>
     </dataValidation>
   </dataValidations>

--- a/AAAGameData/DataTables/TaskReward.xlsx
+++ b/AAAGameData/DataTables/TaskReward.xlsx
@@ -1353,13 +1353,13 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" s="4">
         <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G6" s="4">
         <v>2</v>
@@ -1373,13 +1373,13 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7" s="4">
         <v>20</v>
       </c>
       <c r="F7" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4">
         <v>2</v>
@@ -1399,7 +1399,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4">
         <v>2</v>
@@ -1419,7 +1419,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -1436,7 +1436,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G10" s="4">
         <v>2</v>
@@ -1446,7 +1446,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="E1 F1 G1:AB1">
+    <dataValidation type="list" allowBlank="1" sqref="E1:AB1">
       <formula1>"i18n"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="J3:AB3">

--- a/AAAGameData/DataTables/TaskReward.xlsx
+++ b/AAAGameData/DataTables/TaskReward.xlsx
@@ -703,13 +703,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1245,7 +1245,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.8571428571429" customWidth="1"/>
@@ -1327,45 +1327,45 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:9">
+    <row r="5" customHeight="1" spans="1:9">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3">
-        <v>5</v>
-      </c>
-      <c r="E5" s="4">
-        <v>100</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="1:9">
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="3">
-        <v>10</v>
-      </c>
-      <c r="E6" s="4">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="2">
         <v>2</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7">
@@ -1373,76 +1373,56 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4">
-        <v>20</v>
-      </c>
-      <c r="F7" s="4">
+        <v>30</v>
+      </c>
+      <c r="E7" s="2">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="2">
         <v>2</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3">
-        <v>30</v>
-      </c>
-      <c r="E8" s="4">
-        <v>30</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="C8" s="1"/>
+      <c r="D8">
+        <v>40</v>
+      </c>
+      <c r="E8" s="2">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9">
         <v>5</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9">
-        <v>40</v>
-      </c>
-      <c r="E9" s="4">
-        <v>40</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="D9" s="3">
+        <v>50</v>
+      </c>
+      <c r="E9" s="2">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2">
         <v>2</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3">
-        <v>50</v>
-      </c>
-      <c r="E10" s="4">
-        <v>50</v>
-      </c>
-      <c r="F10" s="4">
-        <v>2</v>
-      </c>
-      <c r="G10" s="4">
-        <v>2</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/AAAGameData/DataTables/TaskReward.xlsx
+++ b/AAAGameData/DataTables/TaskReward.xlsx
@@ -1359,7 +1359,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G6" s="4">
         <v>2</v>
@@ -1379,7 +1379,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G7" s="4">
         <v>2</v>
@@ -1399,7 +1399,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G8" s="4">
         <v>2</v>
@@ -1419,7 +1419,7 @@
         <v>40</v>
       </c>
       <c r="F9" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G9" s="4">
         <v>2</v>
@@ -1436,7 +1436,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G10" s="4">
         <v>2</v>
